--- a/data/Enemy.xlsx
+++ b/data/Enemy.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\GodotProject\2DIncrementGame_Main\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aaaa\demo\2DIncrementGame_Main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="13380"/>
+    <workbookView windowWidth="19200" windowHeight="17655"/>
   </bookViews>
   <sheets>
     <sheet name="Goblins" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="38">
   <si>
     <t>enemyID</t>
   </si>
@@ -97,42 +97,36 @@
     <t>小哥布林</t>
   </si>
   <si>
-    <t>goblin_scout_1</t>
-  </si>
-  <si>
     <t>fast</t>
   </si>
   <si>
     <t>哥布林</t>
   </si>
   <si>
-    <t>goblin_warrior_1</t>
+    <t>大哥布林</t>
   </si>
   <si>
     <t>哥布林斥候</t>
   </si>
   <si>
-    <t>goblin_scout_2</t>
+    <t>哥布林弓箭手</t>
   </si>
   <si>
     <t>哥布林战士</t>
   </si>
   <si>
-    <t>goblin_warrior_2</t>
+    <t>哥布林骑士</t>
+  </si>
+  <si>
+    <t>哥布林法师</t>
   </si>
   <si>
     <t>野蛮哥布林</t>
   </si>
   <si>
-    <t>goblin_scout_3</t>
-  </si>
-  <si>
     <t>哥布林祭祀</t>
   </si>
   <si>
-    <t>goblin_warrior_3</t>
-  </si>
-  <si>
     <t>哥布林boss1</t>
   </si>
   <si>
@@ -148,13 +142,7 @@
     <t>哥布林boss5</t>
   </si>
   <si>
-    <t>goblin_scout_4</t>
-  </si>
-  <si>
     <t>哥布林boss6</t>
-  </si>
-  <si>
-    <t>goblin_warrior_4</t>
   </si>
   <si>
     <t>哥布林boss7</t>
@@ -1207,13 +1195,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H17"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="15.2222222222222" customWidth="1"/>
-    <col min="4" max="5" width="11.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="15.225" customWidth="1"/>
+    <col min="4" max="5" width="11.4416666666667" customWidth="1"/>
     <col min="6" max="6" width="16.6666666666667" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
@@ -1319,13 +1307,10 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>10</v>
-      </c>
-      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" t="s">
         <v>21</v>
-      </c>
-      <c r="H5" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1333,25 +1318,22 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>10</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>10</v>
-      </c>
-      <c r="G6" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1359,25 +1341,22 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>15</v>
-      </c>
-      <c r="G7" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1385,25 +1364,22 @@
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C8">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D8">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1411,25 +1387,22 @@
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C9">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9">
-        <v>8</v>
-      </c>
-      <c r="G9" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1437,25 +1410,22 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C10">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="D10">
+        <v>12</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
         <v>25</v>
       </c>
-      <c r="E10">
-        <v>25</v>
-      </c>
-      <c r="F10">
-        <v>10</v>
-      </c>
-      <c r="G10" t="s">
-        <v>32</v>
-      </c>
       <c r="H10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1463,25 +1433,22 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C11">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E11">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>10</v>
-      </c>
-      <c r="G11" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1489,25 +1456,22 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C12">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="D12">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E12">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F12">
-        <v>10</v>
-      </c>
-      <c r="G12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1515,25 +1479,22 @@
         <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C13">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="D13">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="E13">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="F13">
-        <v>10</v>
-      </c>
-      <c r="G13" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1541,25 +1502,22 @@
         <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C14">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="D14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E14">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F14">
-        <v>10</v>
-      </c>
-      <c r="G14" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1567,25 +1525,22 @@
         <v>11</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C15">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="D15">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E15">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="F15">
         <v>10</v>
       </c>
-      <c r="G15" t="s">
-        <v>38</v>
-      </c>
       <c r="H15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1593,25 +1548,22 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C16">
-        <v>300</v>
+        <v>100</v>
       </c>
       <c r="D16">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E16">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="F16">
-        <v>10</v>
-      </c>
-      <c r="G16" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1619,25 +1571,114 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C17">
+        <v>150</v>
+      </c>
+      <c r="D17">
+        <v>35</v>
+      </c>
+      <c r="E17">
+        <v>30</v>
+      </c>
+      <c r="F17">
+        <v>20</v>
+      </c>
+      <c r="H17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18">
+        <v>200</v>
+      </c>
+      <c r="D18">
+        <v>60</v>
+      </c>
+      <c r="E18">
+        <v>40</v>
+      </c>
+      <c r="F18">
+        <v>15</v>
+      </c>
+      <c r="H18" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19">
+        <v>250</v>
+      </c>
+      <c r="D19">
+        <v>95</v>
+      </c>
+      <c r="E19">
+        <v>50</v>
+      </c>
+      <c r="F19">
+        <v>25</v>
+      </c>
+      <c r="H19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20">
+        <v>300</v>
+      </c>
+      <c r="D20">
+        <v>155</v>
+      </c>
+      <c r="E20">
+        <v>60</v>
+      </c>
+      <c r="F20">
+        <v>20</v>
+      </c>
+      <c r="H20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21">
+        <v>17</v>
+      </c>
+      <c r="B21" t="s">
+        <v>37</v>
+      </c>
+      <c r="C21">
         <v>350</v>
       </c>
-      <c r="D17">
+      <c r="D21">
+        <v>250</v>
+      </c>
+      <c r="E21">
         <v>70</v>
       </c>
-      <c r="E17">
-        <v>70</v>
-      </c>
-      <c r="F17">
-        <v>10</v>
-      </c>
-      <c r="G17" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17" t="s">
-        <v>22</v>
+      <c r="F21">
+        <v>20</v>
+      </c>
+      <c r="H21" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/data/Enemy.xlsx
+++ b/data/Enemy.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\aaaa\demo\2DIncrementGame_Main\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\GodotProject\2DIncrementGame_Main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="17655"/>
+    <workbookView windowWidth="30720" windowHeight="13380"/>
   </bookViews>
   <sheets>
     <sheet name="Goblins" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="41">
   <si>
     <t>enemyID</t>
   </si>
@@ -109,7 +109,7 @@
     <t>哥布林斥候</t>
   </si>
   <si>
-    <t>哥布林弓箭手</t>
+    <t>野蛮哥布林</t>
   </si>
   <si>
     <t>哥布林战士</t>
@@ -118,15 +118,15 @@
     <t>哥布林骑士</t>
   </si>
   <si>
-    <t>哥布林法师</t>
-  </si>
-  <si>
-    <t>野蛮哥布林</t>
-  </si>
-  <si>
     <t>哥布林祭祀</t>
   </si>
   <si>
+    <t>精英哥布林</t>
+  </si>
+  <si>
+    <t>哥布林王</t>
+  </si>
+  <si>
     <t>哥布林boss1</t>
   </si>
   <si>
@@ -146,6 +146,15 @@
   </si>
   <si>
     <t>哥布林boss7</t>
+  </si>
+  <si>
+    <t>哥布林boss8</t>
+  </si>
+  <si>
+    <t>哥布林boss9</t>
+  </si>
+  <si>
+    <t>哥布林boss10</t>
   </si>
 </sst>
 </file>
@@ -1195,13 +1204,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:H24"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="15.225" customWidth="1"/>
-    <col min="4" max="5" width="11.4416666666667" customWidth="1"/>
+    <col min="3" max="3" width="15.2222222222222" customWidth="1"/>
+    <col min="4" max="5" width="11.4444444444444" customWidth="1"/>
     <col min="6" max="6" width="16.6666666666667" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
@@ -1324,7 +1333,7 @@
         <v>10</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E6">
         <v>3</v>
@@ -1344,13 +1353,13 @@
         <v>23</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -1367,10 +1376,10 @@
         <v>24</v>
       </c>
       <c r="C8">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="E8">
         <v>5</v>
@@ -1390,13 +1399,13 @@
         <v>25</v>
       </c>
       <c r="C9">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="D9">
-        <v>9</v>
+        <v>45</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9">
         <v>15</v>
@@ -1413,13 +1422,13 @@
         <v>26</v>
       </c>
       <c r="C10">
-        <v>30</v>
+        <v>400</v>
       </c>
       <c r="D10">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F10">
         <v>25</v>
@@ -1436,13 +1445,13 @@
         <v>27</v>
       </c>
       <c r="C11">
-        <v>35</v>
+        <v>1000</v>
       </c>
       <c r="D11">
-        <v>14</v>
+        <v>85</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F11">
         <v>15</v>
@@ -1459,13 +1468,13 @@
         <v>28</v>
       </c>
       <c r="C12">
-        <v>30</v>
+        <v>2500</v>
       </c>
       <c r="D12">
-        <v>15</v>
+        <v>120</v>
       </c>
       <c r="E12">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F12">
         <v>30</v>
@@ -1482,13 +1491,13 @@
         <v>29</v>
       </c>
       <c r="C13">
-        <v>40</v>
+        <v>8000</v>
       </c>
       <c r="D13">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="E13">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F13">
         <v>20</v>
@@ -1505,13 +1514,13 @@
         <v>30</v>
       </c>
       <c r="C14">
-        <v>80</v>
+        <v>15000</v>
       </c>
       <c r="D14">
-        <v>30</v>
+        <v>270</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F14">
         <v>20</v>
@@ -1531,10 +1540,10 @@
         <v>50</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E15">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F15">
         <v>10</v>
@@ -1551,13 +1560,13 @@
         <v>32</v>
       </c>
       <c r="C16">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="D16">
+        <v>50</v>
+      </c>
+      <c r="E16">
         <v>25</v>
-      </c>
-      <c r="E16">
-        <v>20</v>
       </c>
       <c r="F16">
         <v>15</v>
@@ -1574,13 +1583,13 @@
         <v>33</v>
       </c>
       <c r="C17">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="D17">
+        <v>100</v>
+      </c>
+      <c r="E17">
         <v>35</v>
-      </c>
-      <c r="E17">
-        <v>30</v>
       </c>
       <c r="F17">
         <v>20</v>
@@ -1597,13 +1606,13 @@
         <v>34</v>
       </c>
       <c r="C18">
-        <v>200</v>
+        <v>800</v>
       </c>
       <c r="D18">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="E18">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="F18">
         <v>15</v>
@@ -1620,13 +1629,13 @@
         <v>35</v>
       </c>
       <c r="C19">
-        <v>250</v>
+        <v>2000</v>
       </c>
       <c r="D19">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="E19">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="F19">
         <v>25</v>
@@ -1643,13 +1652,13 @@
         <v>36</v>
       </c>
       <c r="C20">
-        <v>300</v>
+        <v>8000</v>
       </c>
       <c r="D20">
-        <v>155</v>
+        <v>350</v>
       </c>
       <c r="E20">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F20">
         <v>20</v>
@@ -1666,18 +1675,87 @@
         <v>37</v>
       </c>
       <c r="C21">
-        <v>350</v>
+        <v>20000</v>
       </c>
       <c r="D21">
-        <v>250</v>
+        <v>500</v>
       </c>
       <c r="E21">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F21">
         <v>20</v>
       </c>
       <c r="H21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22">
+        <v>60000</v>
+      </c>
+      <c r="D22">
+        <v>800</v>
+      </c>
+      <c r="E22">
+        <v>120</v>
+      </c>
+      <c r="F22">
+        <v>20</v>
+      </c>
+      <c r="H22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23">
+        <v>19</v>
+      </c>
+      <c r="B23" t="s">
+        <v>39</v>
+      </c>
+      <c r="C23">
+        <v>120000</v>
+      </c>
+      <c r="D23">
+        <v>1100</v>
+      </c>
+      <c r="E23">
+        <v>150</v>
+      </c>
+      <c r="F23">
+        <v>20</v>
+      </c>
+      <c r="H23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24">
+        <v>200000</v>
+      </c>
+      <c r="D24">
+        <v>1500</v>
+      </c>
+      <c r="E24">
+        <v>180</v>
+      </c>
+      <c r="F24">
+        <v>20</v>
+      </c>
+      <c r="H24" t="s">
         <v>21</v>
       </c>
     </row>
